--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:21:35+00:00</t>
+    <t>2023-05-26T16:24:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T16:24:55+00:00</t>
+    <t>2023-05-26T18:19:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-26T18:19:44+00:00</t>
+    <t>2023-05-30T15:17:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:17:13+00:00</t>
+    <t>2023-05-30T15:28:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:28:39+00:00</t>
+    <t>2023-05-30T15:33:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:33:40+00:00</t>
+    <t>2023-05-30T15:59:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T15:59:25+00:00</t>
+    <t>2023-05-30T16:40:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:40:03+00:00</t>
+    <t>2023-05-30T16:54:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T16:54:18+00:00</t>
+    <t>2023-05-30T17:00:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:00:44+00:00</t>
+    <t>2023-05-30T17:09:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
+++ b/ig/mc-deploy-1.0.0-ballot/StructureDefinition-as-ext-practitionerrole-registration.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1506" uniqueCount="203">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1346" uniqueCount="194">
   <si>
     <t>Property</t>
   </si>
@@ -24,7 +24,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-registration</t>
+    <t>https://interop.esante.gouv.fr/ig/fhir/annuaire/StructureDefinition/as-ext-practitionerrole-registration</t>
   </si>
   <si>
     <t>Version</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-30T17:09:40+00:00</t>
+    <t>2023-06-08T09:23:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -387,11 +387,13 @@
     <t>Value of extension - must be one of a constrained set of the data types (see [Extensibility](http://hl7.org/fhir/R4/extensibility.html) for a list).</t>
   </si>
   <si>
-    <t xml:space="preserve">type:$this}
-</t>
-  </si>
-  <si>
-    <t>closed</t>
+    <t>required</t>
+  </si>
+  <si>
+    <t>Liste des autorités d'enregistrement.</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J83-AutoriteEnregistrement-RASS/FHIR/JDV-J83-AutoriteEnregistrement-RASS</t>
   </si>
   <si>
     <t>Extension.value[x]</t>
@@ -401,21 +403,6 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:registeringOrganization.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>valueCodeableConcept</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Liste des autorités d'enregistrement.</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J83-AutoriteEnregistrement-RASS/FHIR/JDV-J83-AutoriteEnregistrement-RASS</t>
-  </si>
-  <si>
     <t>Extension.extension:registeringOrganizationDetail</t>
   </si>
   <si>
@@ -438,9 +425,6 @@
   </si>
   <si>
     <t>Extension.extension:registeringOrganizationDetail.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:registeringOrganizationDetail.value[x]:valueCodeableConcept</t>
   </si>
   <si>
     <t>Liste des départements (outre-mer et Monaco inclus).</t>
@@ -474,25 +458,19 @@
 </t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod</t>
-  </si>
-  <si>
-    <t>valuePeriod</t>
-  </si>
-  <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.id</t>
+    <t>Extension.extension:period.value[x].id</t>
   </si>
   <si>
     <t>Extension.extension.value[x].id</t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.extension</t>
+    <t>Extension.extension:period.value[x].extension</t>
   </si>
   <si>
     <t>Extension.extension.value[x].extension</t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.start</t>
+    <t>Extension.extension:period.value[x].start</t>
   </si>
   <si>
     <t>Extension.extension.value[x].start</t>
@@ -524,7 +502,7 @@
     <t>./low</t>
   </si>
   <si>
-    <t>Extension.extension:period.value[x]:valuePeriod.end</t>
+    <t>Extension.extension:period.value[x].end</t>
   </si>
   <si>
     <t>Extension.extension.value[x].end</t>
@@ -572,9 +550,6 @@
     <t>Extension.extension:status.value[x]</t>
   </si>
   <si>
-    <t>Extension.extension:status.value[x]:valueCodeableConcept</t>
-  </si>
-  <si>
     <t>Liste des statuts de l'inscription.</t>
   </si>
   <si>
@@ -603,9 +578,6 @@
   </si>
   <si>
     <t>Extension.extension:hostingDepartment.value[x]</t>
-  </si>
-  <si>
-    <t>Extension.extension:hostingDepartment.value[x]:valueCodeableConcept</t>
   </si>
   <si>
     <t>Extension.extension:isFirst</t>
@@ -940,10 +912,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK45"/>
+  <dimension ref="A1:AK40"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="77.24609375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="56.8671875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="37.25390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="28.14453125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="12.64453125" customWidth="true" bestFit="true" hidden="true"/>
@@ -1886,29 +1858,31 @@
         <v>74</v>
       </c>
       <c r="X9" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y9" t="s" s="2">
-        <v>74</v>
+        <v>122</v>
       </c>
       <c r="Z9" t="s" s="2">
-        <v>74</v>
+        <v>123</v>
       </c>
       <c r="AA9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC9" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>75</v>
@@ -1920,7 +1894,7 @@
         <v>80</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>99</v>
@@ -1928,13 +1902,13 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>117</v>
+        <v>88</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>74</v>
@@ -1956,15 +1930,17 @@
         <v>74</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>119</v>
+        <v>128</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N10" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>129</v>
+      </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
         <v>74</v>
@@ -1989,13 +1965,13 @@
         <v>74</v>
       </c>
       <c r="X10" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y10" t="s" s="2">
-        <v>128</v>
+        <v>74</v>
       </c>
       <c r="Z10" t="s" s="2">
-        <v>129</v>
+        <v>74</v>
       </c>
       <c r="AA10" t="s" s="2">
         <v>74</v>
@@ -2013,22 +1989,22 @@
         <v>74</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK10" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11">
@@ -2036,11 +2012,9 @@
         <v>130</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C11" t="s" s="2">
-        <v>131</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
         <v>74</v>
       </c>
@@ -2061,17 +2035,15 @@
         <v>74</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>132</v>
+        <v>84</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N11" t="s" s="2">
-        <v>133</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N11" s="2"/>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>74</v>
@@ -2120,30 +2092,30 @@
         <v>74</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK11" t="s" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2154,7 +2126,7 @@
         <v>75</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>74</v>
@@ -2166,13 +2138,13 @@
         <v>74</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>84</v>
+        <v>28</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2211,42 +2183,42 @@
         <v>74</v>
       </c>
       <c r="AB12" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC12" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE12" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2254,10 +2226,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>74</v>
@@ -2269,22 +2241,24 @@
         <v>74</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>28</v>
+        <v>112</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N13" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N13" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q13" s="2"/>
       <c r="R13" t="s" s="2">
-        <v>74</v>
+        <v>127</v>
       </c>
       <c r="S13" t="s" s="2">
         <v>74</v>
@@ -2314,42 +2288,42 @@
         <v>74</v>
       </c>
       <c r="AB13" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC13" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE13" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2357,7 +2331,7 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G14" t="s" s="2">
         <v>82</v>
@@ -2372,24 +2346,22 @@
         <v>74</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N14" s="2"/>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q14" s="2"/>
       <c r="R14" t="s" s="2">
-        <v>131</v>
+        <v>74</v>
       </c>
       <c r="S14" t="s" s="2">
         <v>74</v>
@@ -2407,13 +2379,13 @@
         <v>74</v>
       </c>
       <c r="X14" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y14" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="Z14" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AA14" t="s" s="2">
         <v>74</v>
@@ -2431,19 +2403,19 @@
         <v>74</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH14" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK14" t="s" s="2">
         <v>99</v>
@@ -2451,12 +2423,14 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
+        <v>136</v>
+      </c>
+      <c r="B15" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="C15" t="s" s="2">
         <v>137</v>
       </c>
-      <c r="B15" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
         <v>74</v>
       </c>
@@ -2477,13 +2451,13 @@
         <v>74</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>119</v>
+        <v>138</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2522,44 +2496,44 @@
         <v>74</v>
       </c>
       <c r="AB15" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC15" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC15" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C16" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
         <v>74</v>
       </c>
@@ -2580,13 +2554,13 @@
         <v>74</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>120</v>
+        <v>85</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2613,13 +2587,13 @@
         <v>74</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>74</v>
@@ -2637,7 +2611,7 @@
         <v>74</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>75</v>
@@ -2646,25 +2620,23 @@
         <v>82</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C17" t="s" s="2">
-        <v>142</v>
-      </c>
+        <v>108</v>
+      </c>
+      <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
         <v>74</v>
       </c>
@@ -2673,7 +2645,7 @@
         <v>75</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H17" t="s" s="2">
         <v>74</v>
@@ -2688,7 +2660,7 @@
         <v>90</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>143</v>
+        <v>28</v>
       </c>
       <c r="M17" t="s" s="2">
         <v>103</v>
@@ -2730,16 +2702,16 @@
         <v>74</v>
       </c>
       <c r="AB17" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC17" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD17" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE17" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF17" t="s" s="2">
         <v>97</v>
@@ -2762,10 +2734,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2773,7 +2745,7 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G18" t="s" s="2">
         <v>82</v>
@@ -2788,22 +2760,24 @@
         <v>74</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>83</v>
+        <v>111</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>84</v>
+        <v>112</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N18" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N18" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q18" s="2"/>
       <c r="R18" t="s" s="2">
-        <v>74</v>
+        <v>137</v>
       </c>
       <c r="S18" t="s" s="2">
         <v>74</v>
@@ -2845,10 +2819,10 @@
         <v>74</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>86</v>
+        <v>115</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH18" t="s" s="2">
         <v>82</v>
@@ -2860,15 +2834,15 @@
         <v>74</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2879,7 +2853,7 @@
         <v>75</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>74</v>
@@ -2891,13 +2865,13 @@
         <v>74</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>90</v>
+        <v>143</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>28</v>
+        <v>119</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2936,42 +2910,42 @@
         <v>74</v>
       </c>
       <c r="AB19" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ19" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>110</v>
+        <v>145</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2979,7 +2953,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>82</v>
@@ -2994,24 +2968,22 @@
         <v>74</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N20" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N20" s="2"/>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q20" s="2"/>
       <c r="R20" t="s" s="2">
-        <v>142</v>
+        <v>74</v>
       </c>
       <c r="S20" t="s" s="2">
         <v>74</v>
@@ -3053,10 +3025,10 @@
         <v>74</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>82</v>
@@ -3068,26 +3040,26 @@
         <v>74</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="B21" t="s" s="2">
         <v>147</v>
-      </c>
-      <c r="B21" t="s" s="2">
-        <v>117</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>74</v>
+        <v>89</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>74</v>
@@ -3099,15 +3071,17 @@
         <v>74</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>148</v>
+        <v>90</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>119</v>
+        <v>91</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N21" s="2"/>
+        <v>92</v>
+      </c>
+      <c r="N21" t="s" s="2">
+        <v>93</v>
+      </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>74</v>
@@ -3144,29 +3118,31 @@
         <v>74</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC21" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="AC21" t="s" s="2">
+        <v>95</v>
+      </c>
       <c r="AD21" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>99</v>
@@ -3174,14 +3150,12 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
+        <v>148</v>
+      </c>
+      <c r="B22" t="s" s="2">
         <v>149</v>
       </c>
-      <c r="B22" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C22" t="s" s="2">
-        <v>150</v>
-      </c>
+      <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
         <v>74</v>
       </c>
@@ -3199,18 +3173,20 @@
         <v>74</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>119</v>
+        <v>152</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N22" s="2"/>
+        <v>153</v>
+      </c>
+      <c r="N22" t="s" s="2">
+        <v>154</v>
+      </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>74</v>
@@ -3259,7 +3235,7 @@
         <v>74</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>123</v>
+        <v>155</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>75</v>
@@ -3268,21 +3244,21 @@
         <v>82</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>80</v>
+        <v>156</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>99</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3302,23 +3278,27 @@
         <v>74</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>74</v>
+        <v>150</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>84</v>
+        <v>160</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N23" s="2"/>
+        <v>161</v>
+      </c>
+      <c r="N23" t="s" s="2">
+        <v>162</v>
+      </c>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q23" s="2"/>
+      <c r="Q23" t="s" s="2">
+        <v>163</v>
+      </c>
       <c r="R23" t="s" s="2">
         <v>74</v>
       </c>
@@ -3362,7 +3342,7 @@
         <v>74</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>75</v>
@@ -3371,32 +3351,34 @@
         <v>82</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>74</v>
+        <v>156</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>87</v>
+        <v>165</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>154</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C24" t="s" s="2">
+        <v>167</v>
+      </c>
       <c r="D24" t="s" s="2">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
         <v>75</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>74</v>
@@ -3411,13 +3393,13 @@
         <v>90</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>91</v>
+        <v>168</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>92</v>
+        <v>103</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3455,16 +3437,16 @@
         <v>74</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC24" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD24" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF24" t="s" s="2">
         <v>97</v>
@@ -3482,15 +3464,15 @@
         <v>98</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>156</v>
+        <v>106</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3510,20 +3492,18 @@
         <v>74</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>158</v>
+        <v>83</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>159</v>
+        <v>84</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>160</v>
-      </c>
-      <c r="N25" t="s" s="2">
-        <v>161</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N25" s="2"/>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
         <v>74</v>
@@ -3572,7 +3552,7 @@
         <v>74</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>162</v>
+        <v>86</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>75</v>
@@ -3581,21 +3561,21 @@
         <v>82</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>164</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>166</v>
+        <v>108</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3606,7 +3586,7 @@
         <v>75</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>74</v>
@@ -3615,27 +3595,23 @@
         <v>74</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>157</v>
+        <v>74</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>158</v>
+        <v>90</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>167</v>
+        <v>28</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>168</v>
-      </c>
-      <c r="N26" t="s" s="2">
-        <v>169</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N26" s="2"/>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
         <v>74</v>
       </c>
-      <c r="Q26" t="s" s="2">
-        <v>170</v>
-      </c>
+      <c r="Q26" s="2"/>
       <c r="R26" t="s" s="2">
         <v>74</v>
       </c>
@@ -3667,52 +3643,50 @@
         <v>74</v>
       </c>
       <c r="AB26" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC26" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD26" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE26" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>171</v>
+        <v>97</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>163</v>
+        <v>80</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>172</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C27" t="s" s="2">
-        <v>174</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>82</v>
@@ -3727,16 +3701,16 @@
         <v>74</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>175</v>
+        <v>112</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>176</v>
+        <v>114</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -3744,7 +3718,7 @@
       </c>
       <c r="Q27" s="2"/>
       <c r="R27" t="s" s="2">
-        <v>74</v>
+        <v>167</v>
       </c>
       <c r="S27" t="s" s="2">
         <v>74</v>
@@ -3786,30 +3760,30 @@
         <v>74</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI27" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>106</v>
+        <v>117</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3832,13 +3806,13 @@
         <v>74</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3865,13 +3839,13 @@
         <v>74</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>74</v>
+        <v>174</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>74</v>
+        <v>175</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>74</v>
@@ -3889,7 +3863,7 @@
         <v>74</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>75</v>
@@ -3898,23 +3872,25 @@
         <v>82</v>
       </c>
       <c r="AI28" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>87</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C29" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C29" t="s" s="2">
+        <v>177</v>
+      </c>
       <c r="D29" t="s" s="2">
         <v>74</v>
       </c>
@@ -3923,7 +3899,7 @@
         <v>75</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>74</v>
@@ -3938,12 +3914,14 @@
         <v>90</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>28</v>
+        <v>178</v>
       </c>
       <c r="M29" t="s" s="2">
         <v>103</v>
       </c>
-      <c r="N29" s="2"/>
+      <c r="N29" t="s" s="2">
+        <v>179</v>
+      </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>74</v>
@@ -3980,16 +3958,16 @@
         <v>74</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC29" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD29" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF29" t="s" s="2">
         <v>97</v>
@@ -4012,10 +3990,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4023,7 +4001,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>82</v>
@@ -4038,24 +4016,22 @@
         <v>74</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>112</v>
+        <v>84</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N30" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>85</v>
+      </c>
+      <c r="N30" s="2"/>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q30" s="2"/>
       <c r="R30" t="s" s="2">
-        <v>174</v>
+        <v>74</v>
       </c>
       <c r="S30" t="s" s="2">
         <v>74</v>
@@ -4097,10 +4073,10 @@
         <v>74</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>115</v>
+        <v>86</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>82</v>
@@ -4112,15 +4088,15 @@
         <v>74</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -4131,7 +4107,7 @@
         <v>75</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>74</v>
@@ -4143,13 +4119,13 @@
         <v>74</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>118</v>
+        <v>90</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>119</v>
+        <v>28</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>120</v>
+        <v>103</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4188,50 +4164,50 @@
         <v>74</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC31" s="2"/>
+        <v>94</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>95</v>
+      </c>
       <c r="AD31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE31" t="s" s="2">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>124</v>
+        <v>98</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C32" t="s" s="2">
-        <v>126</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>82</v>
@@ -4246,22 +4222,24 @@
         <v>74</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N32" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N32" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
-        <v>74</v>
+        <v>177</v>
       </c>
       <c r="S32" t="s" s="2">
         <v>74</v>
@@ -4279,13 +4257,13 @@
         <v>74</v>
       </c>
       <c r="X32" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y32" t="s" s="2">
-        <v>182</v>
+        <v>74</v>
       </c>
       <c r="Z32" t="s" s="2">
-        <v>183</v>
+        <v>74</v>
       </c>
       <c r="AA32" t="s" s="2">
         <v>74</v>
@@ -4303,19 +4281,19 @@
         <v>74</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK32" t="s" s="2">
         <v>99</v>
@@ -4323,14 +4301,12 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>185</v>
-      </c>
+        <v>117</v>
+      </c>
+      <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
         <v>74</v>
       </c>
@@ -4351,17 +4327,15 @@
         <v>74</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>90</v>
+        <v>118</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>186</v>
+        <v>119</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N33" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>120</v>
+      </c>
+      <c r="N33" s="2"/>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
         <v>74</v>
@@ -4386,13 +4360,13 @@
         <v>74</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>74</v>
+        <v>121</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>74</v>
+        <v>134</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>74</v>
+        <v>135</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>74</v>
@@ -4410,32 +4384,34 @@
         <v>74</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>97</v>
+        <v>124</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH33" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI33" t="s" s="2">
         <v>80</v>
       </c>
       <c r="AJ33" t="s" s="2">
-        <v>98</v>
+        <v>125</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>106</v>
-      </c>
-      <c r="C34" s="2"/>
+        <v>88</v>
+      </c>
+      <c r="C34" t="s" s="2">
+        <v>185</v>
+      </c>
       <c r="D34" t="s" s="2">
         <v>74</v>
       </c>
@@ -4456,15 +4432,17 @@
         <v>74</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>84</v>
+        <v>186</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>85</v>
-      </c>
-      <c r="N34" s="2"/>
+        <v>103</v>
+      </c>
+      <c r="N34" t="s" s="2">
+        <v>187</v>
+      </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
         <v>74</v>
@@ -4513,30 +4491,30 @@
         <v>74</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ34" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>87</v>
+        <v>74</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4547,7 +4525,7 @@
         <v>75</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>74</v>
@@ -4559,13 +4537,13 @@
         <v>74</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>90</v>
+        <v>83</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>28</v>
+        <v>84</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>103</v>
+        <v>85</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4604,42 +4582,42 @@
         <v>74</v>
       </c>
       <c r="AB35" t="s" s="2">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>95</v>
+        <v>74</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>96</v>
+        <v>74</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>75</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI35" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ35" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>74</v>
+        <v>87</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4647,10 +4625,10 @@
       </c>
       <c r="E36" s="2"/>
       <c r="F36" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="G36" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H36" t="s" s="2">
         <v>74</v>
@@ -4662,24 +4640,22 @@
         <v>74</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>112</v>
+        <v>28</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>114</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q36" s="2"/>
       <c r="R36" t="s" s="2">
-        <v>185</v>
+        <v>74</v>
       </c>
       <c r="S36" t="s" s="2">
         <v>74</v>
@@ -4709,42 +4685,42 @@
         <v>74</v>
       </c>
       <c r="AB36" t="s" s="2">
-        <v>74</v>
+        <v>94</v>
       </c>
       <c r="AC36" t="s" s="2">
-        <v>74</v>
+        <v>95</v>
       </c>
       <c r="AD36" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE36" t="s" s="2">
-        <v>74</v>
+        <v>96</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>115</v>
+        <v>97</v>
       </c>
       <c r="AG36" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="AH36" t="s" s="2">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>99</v>
+        <v>74</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -4752,7 +4728,7 @@
       </c>
       <c r="E37" s="2"/>
       <c r="F37" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G37" t="s" s="2">
         <v>82</v>
@@ -4767,22 +4743,24 @@
         <v>74</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>118</v>
+        <v>111</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>119</v>
+        <v>112</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N37" s="2"/>
+        <v>113</v>
+      </c>
+      <c r="N37" t="s" s="2">
+        <v>114</v>
+      </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="Q37" s="2"/>
       <c r="R37" t="s" s="2">
-        <v>74</v>
+        <v>185</v>
       </c>
       <c r="S37" t="s" s="2">
         <v>74</v>
@@ -4812,29 +4790,31 @@
         <v>74</v>
       </c>
       <c r="AB37" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="AC37" s="2"/>
+        <v>74</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>74</v>
+      </c>
       <c r="AD37" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AE37" t="s" s="2">
-        <v>122</v>
+        <v>74</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="AG37" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH37" t="s" s="2">
         <v>82</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>124</v>
+        <v>74</v>
       </c>
       <c r="AK37" t="s" s="2">
         <v>99</v>
@@ -4842,14 +4822,12 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B38" t="s" s="2">
         <v>117</v>
       </c>
-      <c r="C38" t="s" s="2">
-        <v>126</v>
-      </c>
+      <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
         <v>74</v>
       </c>
@@ -4870,7 +4848,7 @@
         <v>74</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>118</v>
+        <v>192</v>
       </c>
       <c r="L38" t="s" s="2">
         <v>119</v>
@@ -4903,13 +4881,13 @@
         <v>74</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>127</v>
+        <v>74</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>139</v>
+        <v>74</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>140</v>
+        <v>74</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>74</v>
@@ -4927,7 +4905,7 @@
         <v>74</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>75</v>
@@ -4939,7 +4917,7 @@
         <v>80</v>
       </c>
       <c r="AJ38" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AK38" t="s" s="2">
         <v>99</v>
@@ -4947,20 +4925,18 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>193</v>
+        <v>115</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="C39" t="s" s="2">
-        <v>194</v>
-      </c>
+        <v>115</v>
+      </c>
+      <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
         <v>74</v>
       </c>
       <c r="E39" s="2"/>
       <c r="F39" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="G39" t="s" s="2">
         <v>82</v>
@@ -4975,16 +4951,16 @@
         <v>74</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>90</v>
+        <v>111</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>195</v>
+        <v>112</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>196</v>
+        <v>114</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -4992,7 +4968,7 @@
       </c>
       <c r="Q39" s="2"/>
       <c r="R39" t="s" s="2">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="S39" t="s" s="2">
         <v>74</v>
@@ -5034,30 +5010,30 @@
         <v>74</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="AG39" t="s" s="2">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="AH39" t="s" s="2">
-        <v>76</v>
+        <v>82</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="AJ39" t="s" s="2">
-        <v>98</v>
+        <v>74</v>
       </c>
       <c r="AK39" t="s" s="2">
-        <v>74</v>
+        <v>99</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>197</v>
+        <v>124</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5068,7 +5044,7 @@
         <v>75</v>
       </c>
       <c r="G40" t="s" s="2">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="H40" t="s" s="2">
         <v>74</v>
@@ -5080,13 +5056,13 @@
         <v>74</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>83</v>
+        <v>193</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>85</v>
+        <v>120</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -5137,7 +5113,7 @@
         <v>74</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>86</v>
+        <v>124</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>75</v>
@@ -5146,531 +5122,12 @@
         <v>82</v>
       </c>
       <c r="AI40" t="s" s="2">
-        <v>74</v>
+        <v>80</v>
       </c>
       <c r="AJ40" t="s" s="2">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="s" s="2">
-        <v>198</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>108</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>90</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>28</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>103</v>
-      </c>
-      <c r="N41" s="2"/>
-      <c r="O41" s="2"/>
-      <c r="P41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>94</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>95</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>96</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>97</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>98</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="s" s="2">
-        <v>199</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>110</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O42" s="2"/>
-      <c r="P42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>194</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="s" s="2">
-        <v>200</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>117</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>201</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" s="2"/>
-      <c r="P43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>111</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>112</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>113</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>114</v>
-      </c>
-      <c r="O44" s="2"/>
-      <c r="P44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>115</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>202</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>119</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>120</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" s="2"/>
-      <c r="P45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>74</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>123</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>75</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>82</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>124</v>
-      </c>
-      <c r="AK45" t="s" s="2">
         <v>99</v>
       </c>
     </row>
